--- a/DOSSIES_MULTIFORMATO/CBMAM/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/CBMAM/dossie.xlsx
@@ -636,7 +636,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2020NE00849</t>
+          <t>2020NE00850</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>107.7</v>
+        <v>1148.11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2020NE00850</t>
+          <t>2020NE00849</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -672,7 +672,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1148.11</v>
+        <v>107.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -860,7 +860,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2018NE01192</t>
+          <t>2018NE01193</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1210.56</v>
+        <v>4196.65</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2018NE01193</t>
+          <t>2018NE01192</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4196.65</v>
+        <v>1210.56</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -912,14 +912,10 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2016NE00692</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>5/2016</t>
-        </is>
-      </c>
+          <t>2016NE00691</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>28/12/2016</t>
@@ -935,17 +931,21 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>serviços de processamento de dados para o CBMAM.</t>
+          <t>Anulação da Ne nº 687 por incorreção na fonte de recursos</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2016NE00691</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
+          <t>2016NE00692</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5/2016</t>
+        </is>
+      </c>
       <c r="C13" t="inlineStr">
         <is>
           <t>28/12/2016</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Anulação da Ne nº 687 por incorreção na fonte de recursos</t>
+          <t>serviços de processamento de dados para o CBMAM.</t>
         </is>
       </c>
     </row>
@@ -971,11 +971,7 @@
           <t>2016NE00520</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2/2011</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>28/09/2016</t>
@@ -1001,7 +997,11 @@
           <t>2016NE00520</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>28/09/2016</t>
@@ -1024,12 +1024,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2019NE00234</t>
+          <t>2019NE00237</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>5/2016</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1038,7 +1038,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2780.74</v>
+        <v>351.75</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1047,24 +1047,28 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Serviço de execução de sistema de informação para a disponibilização do sistema de protocolo em plataforma web (SPROWEB), para controle e acompanhamento do registro de todos os documentos ou processos</t>
+          <t>Processo de reconhecimento de dívida do mês de DEZ 2018, referente ao 2º Termo Aditivo ao Contrato nº005/2016 pelo serviço de Controle de Pessoal para o CBMAM (CPBM).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2019NE00239</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
+          <t>2019NE00235</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5/2016</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
           <t>28/05/2019</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2780.74</v>
+        <v>351.75</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1073,14 +1077,14 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cancelamento total do Empenho para inclusão de informação da vigência na descrição do item.</t>
+          <t>Processo de reconhecimento de dívida do mês de OUT 2018, referente ao 2º Termo Aditivo ao Contrato nº005/2016 pelo serviço de Controle de Pessoal para o CBMAM (CPBM).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2019NE00232</t>
+          <t>2019NE00233</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1106,12 +1110,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2019NE00236</t>
+          <t>2019NE00240</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1120,7 +1124,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>351.75</v>
+        <v>2780.74</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1129,19 +1133,19 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Processo de reconhecimento de dívida do mês de NOV 2018, referente ao 2º Termo Aditivo ao Contrato nº005/2016 pelo serviço de Controle de Pessoal para o CBMAM (CPBM).</t>
+          <t>Serviço de execução de sistema de informação para a disponibilização do sistema de protocolo em plataforma web (SPROWEB), para controle e acompanhamento do registro de todos os documentos ou processos</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2019NE00240</t>
+          <t>2019NE00236</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>5/2016</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1150,7 +1154,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2780.74</v>
+        <v>351.75</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1159,14 +1163,14 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Serviço de execução de sistema de informação para a disponibilização do sistema de protocolo em plataforma web (SPROWEB), para controle e acompanhamento do registro de todos os documentos ou processos</t>
+          <t>Processo de reconhecimento de dívida do mês de NOV 2018, referente ao 2º Termo Aditivo ao Contrato nº005/2016 pelo serviço de Controle de Pessoal para o CBMAM (CPBM).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2019NE00233</t>
+          <t>2019NE00232</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1192,21 +1196,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2019NE00235</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>5/2016</t>
-        </is>
-      </c>
+          <t>2019NE00239</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>28/05/2019</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>351.75</v>
+        <v>2780.74</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1215,19 +1215,19 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Processo de reconhecimento de dívida do mês de OUT 2018, referente ao 2º Termo Aditivo ao Contrato nº005/2016 pelo serviço de Controle de Pessoal para o CBMAM (CPBM).</t>
+          <t>Cancelamento total do Empenho para inclusão de informação da vigência na descrição do item.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2019NE00237</t>
+          <t>2019NE00234</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>351.75</v>
+        <v>2780.74</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1245,14 +1245,14 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Processo de reconhecimento de dívida do mês de DEZ 2018, referente ao 2º Termo Aditivo ao Contrato nº005/2016 pelo serviço de Controle de Pessoal para o CBMAM (CPBM).</t>
+          <t>Serviço de execução de sistema de informação para a disponibilização do sistema de protocolo em plataforma web (SPROWEB), para controle e acompanhamento do registro de todos os documentos ou processos</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2016NE00243</t>
+          <t>2016NE00248</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4212.27</v>
+        <v>3369.82</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1275,14 +1275,14 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tal solicitação visa atender demanda oriunda do processo 022104.000227/2014 referente a pagamento de despesas de exercício anteriores.</t>
+          <t>Tal solicitação visa atender demanda oriunda do processo 022104.000219/2015 referente a pagamento de despesas de exercício anteriores.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2016NE00245</t>
+          <t>2016NE00247</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1342,7 +1342,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2016NE00247</t>
+          <t>2016NE00245</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1372,7 +1372,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2016NE00248</t>
+          <t>2016NE00243</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>3369.82</v>
+        <v>4212.27</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tal solicitação visa atender demanda oriunda do processo 022104.000219/2015 referente a pagamento de despesas de exercício anteriores.</t>
+          <t>Tal solicitação visa atender demanda oriunda do processo 022104.000227/2014 referente a pagamento de despesas de exercício anteriores.</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1517,11 @@
           <t>2016NE00575</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
           <t>27/10/2016</t>
@@ -1543,11 +1547,7 @@
           <t>2016NE00575</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2/2011</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>27/10/2016</t>
@@ -1570,7 +1570,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2019NE00220</t>
+          <t>2019NE00219</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1589,14 +1589,14 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>esta solicitação visa atender demanda do processo numero 024/2019.</t>
+          <t>esta solicitação visa atender demanda do processo numero 015/2019.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2019NE00219</t>
+          <t>2019NE00220</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -1615,7 +1615,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>esta solicitação visa atender demanda do processo numero 015/2019.</t>
+          <t>esta solicitação visa atender demanda do processo numero 024/2019.</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2015NE00414</t>
+          <t>2015NE00415</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1662,7 +1662,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>4212.27</v>
+        <v>17747.71</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Despesas de Teleprocessamento</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE LINK DE COMUNICAÇÃO</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2015NE00415</t>
+          <t>2015NE00414</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>17747.71</v>
+        <v>4212.27</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE LINK DE COMUNICAÇÃO</t>
+          <t>Despesas de Teleprocessamento</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2015NE00411</t>
+          <t>2015NE00413</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -1783,14 +1783,14 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS</t>
+          <t>Servico de Processamento</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2015NE00413</t>
+          <t>2015NE00411</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Servico de Processamento</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE PROCESSAMENTO DE DADOS</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2015NE00592</t>
+          <t>2015NE00591</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1912,7 +1912,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2483.82</v>
+        <v>8424.540000000001</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2015NE00591</t>
+          <t>2015NE00592</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>8424.540000000001</v>
+        <v>2483.82</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2015NE00408</t>
+          <t>2015NE00410</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -2076,7 +2076,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1241.91</v>
+        <v>4212.27</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2085,14 +2085,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>TAL SOLICITAÇÃO VISA ATENDER PAGAMENTO PARCIAL DE PROCESSO 22104.000116/2015 REFERENTE A CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO SERVIÇO DE PROCESSAMENTO DE DADOS - PRODAM</t>
+          <t>Anulação total da NE por falta de informação na Descrição.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2015NE00409</t>
+          <t>2015NE00407</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1241.91</v>
+        <v>4212.27</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2111,14 +2111,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Anulação total na NE por falta de informação na descrição.</t>
+          <t>Serviço de acesso a internet e ao computador central da PRODAM, com velocidade de 256Kbps. com reajuste de 6,24 do contrato primitivo conforme cláusula décima primeira. Restando 39.033,71 a ser empenh</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2015NE00407</t>
+          <t>2015NE00409</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -2128,7 +2128,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4212.27</v>
+        <v>1241.91</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2137,14 +2137,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Serviço de acesso a internet e ao computador central da PRODAM, com velocidade de 256Kbps. com reajuste de 6,24 do contrato primitivo conforme cláusula décima primeira. Restando 39.033,71 a ser empenh</t>
+          <t>Anulação total na NE por falta de informação na descrição.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2015NE00410</t>
+          <t>2015NE00408</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4212.27</v>
+        <v>1241.91</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Anulação total da NE por falta de informação na Descrição.</t>
+          <t>TAL SOLICITAÇÃO VISA ATENDER PAGAMENTO PARCIAL DE PROCESSO 22104.000116/2015 REFERENTE A CONTRATAÇÃO DE EMPRESA ESPECIALIZADA NO SERVIÇO DE PROCESSAMENTO DE DADOS - PRODAM</t>
         </is>
       </c>
     </row>
@@ -2230,12 +2230,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2018NE00605</t>
+          <t>2018NE00607</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2244,7 +2244,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2421.12</v>
+        <v>18088.63</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2253,19 +2253,19 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Serviço de controle de pessoal para o CBMAM(CPBM).</t>
+          <t>Serviço de execução de sistemas de informação de protocolo em plataforma web (sproweb).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2018NE00607</t>
+          <t>2018NE00605</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>5/2016</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2274,7 +2274,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>18088.63</v>
+        <v>2421.12</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2283,17 +2283,21 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Serviço de execução de sistemas de informação de protocolo em plataforma web (sproweb).</t>
+          <t>Serviço de controle de pessoal para o CBMAM(CPBM).</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2021NE0000003</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>2021NE0000002</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>5/2016</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
           <t>20/01/2021</t>
@@ -2309,21 +2313,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Anulação para correção da Data de emissão para 04/01/2020.</t>
+          <t>Serviço de processamento do Sistema de Controle de pessoal para o CBMAM (CPBM).</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2021NE0000002</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>5/2016</t>
-        </is>
-      </c>
+          <t>2021NE0000003</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
           <t>20/01/2021</t>
@@ -2339,19 +2339,19 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Serviço de processamento do Sistema de Controle de pessoal para o CBMAM (CPBM).</t>
+          <t>Anulação para correção da Data de emissão para 04/01/2020.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2019NE00402</t>
+          <t>2019NE00401</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>5/2016</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2360,7 +2360,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5168.18</v>
+        <v>899.9400000000001</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2369,19 +2369,19 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Serviço de execução de sistemas de informação de protocolo em plataforma web (sproweb)</t>
+          <t>Serviço de controle de pessoal para o CBMAM(CPBM).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2019NE00401</t>
+          <t>2019NE00402</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>899.9400000000001</v>
+        <v>5168.18</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Serviço de controle de pessoal para o CBMAM(CPBM).</t>
+          <t>Serviço de execução de sistemas de informação de protocolo em plataforma web (sproweb)</t>
         </is>
       </c>
     </row>
@@ -2574,7 +2574,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2020NE00427</t>
+          <t>2020NE00432</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>19465.18</v>
+        <v>2780.74</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2020NE00431</t>
+          <t>2020NE00426</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>873.78</v>
+        <v>2621.34</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2020NE00426</t>
+          <t>2020NE00431</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2621.34</v>
+        <v>873.78</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2020NE00432</t>
+          <t>2020NE00427</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2780.74</v>
+        <v>19465.18</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -2694,12 +2694,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2019NE00559</t>
+          <t>2019NE00560</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>5/2016</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>9418.370000000001</v>
+        <v>980.73</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -2717,19 +2717,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Serviço de execução de sistema de informação para a disponibilização do sistema de protocolo em plataforma web (SPROWEB)</t>
+          <t>Serviço de processamento do Sistema de Controle de pessoal para o CBMAM (CPBM).</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2019NE00560</t>
+          <t>2019NE00559</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2738,7 +2738,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>980.73</v>
+        <v>9418.370000000001</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -2747,14 +2747,14 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Serviço de processamento do Sistema de Controle de pessoal para o CBMAM (CPBM).</t>
+          <t>Serviço de execução de sistema de informação para a disponibilização do sistema de protocolo em plataforma web (SPROWEB)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2016NE00571</t>
+          <t>2016NE00570</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -2773,21 +2773,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Reforço da Ne 054 para liquidação dos serviços do mes de Julho de 2016</t>
+          <t>ANULAÇÃO NE 556 POR ESTAR COMO REFORÇAR E O MESMO NÃO O SER.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2016NE00571</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2/2011</t>
-        </is>
-      </c>
+          <t>2016NE00570</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
           <t>17/10/2016</t>
@@ -2803,17 +2799,21 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Reforço da Ne 054 para liquidação dos serviços do mes de Julho de 2016</t>
+          <t>ANULAÇÃO NE 556 POR ESTAR COMO REFORÇAR E O MESMO NÃO O SER.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2016NE00570</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>2016NE00571</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
           <t>17/10/2016</t>
@@ -2829,14 +2829,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>ANULAÇÃO NE 556 POR ESTAR COMO REFORÇAR E O MESMO NÃO O SER.</t>
+          <t>Reforço da Ne 054 para liquidação dos serviços do mes de Julho de 2016</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2016NE00570</t>
+          <t>2016NE00571</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
@@ -2855,14 +2855,14 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>ANULAÇÃO NE 556 POR ESTAR COMO REFORÇAR E O MESMO NÃO O SER.</t>
+          <t>Reforço da Ne 054 para liquidação dos serviços do mes de Julho de 2016</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2018NE00235</t>
+          <t>2018NE00236</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2876,7 +2876,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11220</v>
+        <v>29920</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -2885,14 +2885,14 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>PROCESSO DE RECONHECIMENTO DE DÍVIDA DO PAGAMENTO DE FATURAS REFERENTE AO SERVIÇO DE ACESSO A INTERNET DOS MESES DE OUTUBRO A DEZEMBRO.</t>
+          <t>PROCESSO DE RECONHECIMENTO DE DÍVIDA DO PAGAMENTO DE FATURAS REFERENTE AO SERVIÇO DE ACESSO A INTERNET DOS MESES DE JANEIRO A AGOSTO DE 2017.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2018NE00236</t>
+          <t>2018NE00235</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2906,7 +2906,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>29920</v>
+        <v>11220</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>PROCESSO DE RECONHECIMENTO DE DÍVIDA DO PAGAMENTO DE FATURAS REFERENTE AO SERVIÇO DE ACESSO A INTERNET DOS MESES DE JANEIRO A AGOSTO DE 2017.</t>
+          <t>PROCESSO DE RECONHECIMENTO DE DÍVIDA DO PAGAMENTO DE FATURAS REFERENTE AO SERVIÇO DE ACESSO A INTERNET DOS MESES DE OUTUBRO A DEZEMBRO.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2948,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2020NE00419</t>
+          <t>2020NE00416</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
@@ -2958,7 +2958,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>2621.34</v>
+        <v>1085.76</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3000,7 +3000,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2020NE00416</t>
+          <t>2020NE00419</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1085.76</v>
+        <v>2621.34</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3168,17 +3168,21 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2016NE00555</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
+          <t>2016NE00556</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
       <c r="C92" t="inlineStr">
         <is>
           <t>14/10/2016</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>4684.8</v>
+        <v>3369.82</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3187,24 +3191,28 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 054 POR VALOR MENSAL ESTAR ACIMA DO DESCRITO NO CONTRATO (ERRO DO REFORÇO NE 520)</t>
+          <t xml:space="preserve">5º Termo aditivo ao contrato nº 002/2011 Processo nº 219/2015. Vigencia 08/10/2015 a 08/10/2016. Valor mensal: R$ 3.369,82 Valor Global R$ 40.437,84 NE ref. reforço NE 054 para Julho/2016. Fundamento </t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2016NE00555</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
+          <t>2016NE00556</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2/2011</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
           <t>14/10/2016</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>4684.8</v>
+        <v>3369.82</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3213,28 +3221,24 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>ANULAÇÃO PARCIAL DA NE 054 POR VALOR MENSAL ESTAR ACIMA DO DESCRITO NO CONTRATO (ERRO DO REFORÇO NE 520)</t>
+          <t xml:space="preserve">5º Termo aditivo ao contrato nº 002/2011 Processo nº 219/2015. Vigencia 08/10/2015 a 08/10/2016. Valor mensal: R$ 3.369,82 Valor Global R$ 40.437,84 NE ref. reforço NE 054 para Julho/2016. Fundamento </t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2016NE00556</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2/2011</t>
-        </is>
-      </c>
+          <t>2016NE00555</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
           <t>14/10/2016</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>3369.82</v>
+        <v>4684.8</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3243,28 +3247,24 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t xml:space="preserve">5º Termo aditivo ao contrato nº 002/2011 Processo nº 219/2015. Vigencia 08/10/2015 a 08/10/2016. Valor mensal: R$ 3.369,82 Valor Global R$ 40.437,84 NE ref. reforço NE 054 para Julho/2016. Fundamento </t>
+          <t>ANULAÇÃO PARCIAL DA NE 054 POR VALOR MENSAL ESTAR ACIMA DO DESCRITO NO CONTRATO (ERRO DO REFORÇO NE 520)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2016NE00556</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2/2011</t>
-        </is>
-      </c>
+          <t>2016NE00555</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
           <t>14/10/2016</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>3369.82</v>
+        <v>4684.8</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t xml:space="preserve">5º Termo aditivo ao contrato nº 002/2011 Processo nº 219/2015. Vigencia 08/10/2015 a 08/10/2016. Valor mensal: R$ 3.369,82 Valor Global R$ 40.437,84 NE ref. reforço NE 054 para Julho/2016. Fundamento </t>
+          <t>ANULAÇÃO PARCIAL DA NE 054 POR VALOR MENSAL ESTAR ACIMA DO DESCRITO NO CONTRATO (ERRO DO REFORÇO NE 520)</t>
         </is>
       </c>
     </row>
@@ -3628,12 +3628,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2018NE00039</t>
+          <t>2018NE00040</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>2421.12</v>
+        <v>12920.45</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -3651,19 +3651,19 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE MANUTENÇÃO DO SISTEMA DE PROCESSAMENTO DE CONTROLE DE PESSOAL DA DIRETORIA DE RECURSOS HUMANOS DO CBMAM</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE INFORMAÇÃO PARA DISPONIBILIZAÇÃO DOS SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2018NE00040</t>
+          <t>2018NE00039</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>5/2016</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>12920.45</v>
+        <v>2421.12</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE INFORMAÇÃO PARA DISPONIBILIZAÇÃO DOS SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE MANUTENÇÃO DO SISTEMA DE PROCESSAMENTO DE CONTROLE DE PESSOAL DA DIRETORIA DE RECURSOS HUMANOS DO CBMAM</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2018NE01179</t>
+          <t>2018NE01177</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
@@ -3724,7 +3724,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>6366.47</v>
+        <v>159.16</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -3740,7 +3740,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2018NE01178</t>
+          <t>2018NE01176</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>7147.07</v>
+        <v>323.22</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2018NE01176</t>
+          <t>2018NE01178</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
@@ -3776,7 +3776,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>323.22</v>
+        <v>7147.07</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2018NE01177</t>
+          <t>2018NE01179</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>159.16</v>
+        <v>6366.47</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3818,12 +3818,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2017NE01557</t>
+          <t>2017NE01556</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>5/2016</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2584.09</v>
+        <v>403.52</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -3841,19 +3841,19 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE INFORMAÇÃO PARA DISPONIBILIZAÇÃO DOS SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE MANUTENÇÃO DO SISTEMA DE PROCESSAMENTO DE CONTROLE DE PESSOAL DA DIRETORIA DE RECURSOS HUMANOS DO CBMAM</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2017NE01556</t>
+          <t>2017NE01557</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3862,7 +3862,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>403.52</v>
+        <v>2584.09</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -3871,7 +3871,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE MANUTENÇÃO DO SISTEMA DE PROCESSAMENTO DE CONTROLE DE PESSOAL DA DIRETORIA DE RECURSOS HUMANOS DO CBMAM</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE INFORMAÇÃO PARA DISPONIBILIZAÇÃO DOS SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
@@ -3908,12 +3908,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2020NE00270</t>
+          <t>2020NE00271</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>5/2016</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>19465.18</v>
+        <v>2621.34</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -3931,19 +3931,19 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Serviço de execução de sistema de informação para a disponibilização do sistema de protocolo em plataforma web (SPROWEB), para controle e acompanhamento do registro de todos os documentos ou processos</t>
+          <t>Serviço de processamento do Sistema de Controle de pessoal para o CBMAM (CPBM).</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2020NE00271</t>
+          <t>2020NE00270</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>2621.34</v>
+        <v>19465.18</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Serviço de processamento do Sistema de Controle de pessoal para o CBMAM (CPBM).</t>
+          <t>Serviço de execução de sistema de informação para a disponibilização do sistema de protocolo em plataforma web (SPROWEB), para controle e acompanhamento do registro de todos os documentos ou processos</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2015NE00033</t>
+          <t>2015NE00038</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>ref. ao 3º Termo Aditivo ao Contrato nº 06/2011, com valor Global de R$ 4.967,64 e valor mensal de R$ 413,97 com vigência de 12 meses Fundamentado pelo Art.24; II; Lei 8.666/93</t>
+          <t>Cobertura financeira 2015-meses: janeiro a março.</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2015NE00038</t>
+          <t>2015NE00033</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Cobertura financeira 2015-meses: janeiro a março.</t>
+          <t>ref. ao 3º Termo Aditivo ao Contrato nº 06/2011, com valor Global de R$ 4.967,64 e valor mensal de R$ 413,97 com vigência de 12 meses Fundamentado pelo Art.24; II; Lei 8.666/93</t>
         </is>
       </c>
     </row>
@@ -4238,12 +4238,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2021NE0000026</t>
+          <t>2021NE0000027</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4252,7 +4252,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>2621.34</v>
+        <v>13903.7</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -4261,19 +4261,19 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Serviço de processamento do Sistema de Controle de pessoal para o CBMAM (CPBM).</t>
+          <t>Serviço de execução de sistema de informação para a disponibilização do sistema de protocolo em plataforma web (SPROWEB), para controle e acompanhamento do registro de todos os documentos ou processos</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2021NE0000027</t>
+          <t>2021NE0000026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>5/2016</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4282,7 +4282,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>13903.7</v>
+        <v>2621.34</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -4291,14 +4291,14 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Serviço de execução de sistema de informação para a disponibilização do sistema de protocolo em plataforma web (SPROWEB), para controle e acompanhamento do registro de todos os documentos ou processos</t>
+          <t>Serviço de processamento do Sistema de Controle de pessoal para o CBMAM (CPBM).</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2016NE00046</t>
+          <t>2016NE00054</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>82363 - SERVIÇO DE LINK DE COMUNICAÇÃO, Descrição: SERVIÇO DE LINK DE COMUNICAÇÃO, Descrição: Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados</t>
+          <t>SERVIÇO DE ACESSO A INTERNET</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2016NE00054</t>
+          <t>2016NE00046</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SERVIÇO DE ACESSO A INTERNET</t>
+          <t>82363 - SERVIÇO DE LINK DE COMUNICAÇÃO, Descrição: SERVIÇO DE LINK DE COMUNICAÇÃO, Descrição: Contratação de serviços técnicos especializados em telecomunicações para disponibilização de link de dados</t>
         </is>
       </c>
     </row>
@@ -4440,14 +4440,10 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2024NE0000010</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>6/2021</t>
-        </is>
-      </c>
+          <t>2024NE0000008</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
           <t>02/01/2024</t>
@@ -4470,10 +4466,14 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2024NE0000008</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr"/>
+          <t>2024NE0000010</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>6/2021</t>
+        </is>
+      </c>
       <c r="C137" t="inlineStr">
         <is>
           <t>02/01/2024</t>
@@ -4526,12 +4526,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2020NE00004</t>
+          <t>2020NE00003</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>5/2016</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4540,7 +4540,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>13903.7</v>
+        <v>2621.34</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -4549,19 +4549,19 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Serviço de execução de sistema de informação para a disponibilização do sistema de protocolo em plataforma web (SPROWEB), para controle e acompanhamento do registro de todos os documentos ou processos</t>
+          <t>Serviço de processamento do Sistema de Controle de pessoal para o CBMAM (CPBM).</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2020NE00003</t>
+          <t>2020NE00004</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4570,7 +4570,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>2621.34</v>
+        <v>13903.7</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -4579,19 +4579,19 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Serviço de processamento do Sistema de Controle de pessoal para o CBMAM (CPBM).</t>
+          <t>Serviço de execução de sistema de informação para a disponibilização do sistema de protocolo em plataforma web (SPROWEB), para controle e acompanhamento do registro de todos os documentos ou processos</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2019NE00004</t>
+          <t>2019NE00003</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>5/2016</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4600,7 +4600,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>7752.27</v>
+        <v>1210.56</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -4609,19 +4609,19 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Serviço de execução de sistemas de informação de protocolo em plataforma web (sproweb).</t>
+          <t>Serviço de controle de pessoal para o CBMAM(CPBM).</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2019NE00003</t>
+          <t>2019NE00004</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1210.56</v>
+        <v>7752.27</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -4639,19 +4639,19 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Serviço de controle de pessoal para o CBMAM(CPBM).</t>
+          <t>Serviço de execução de sistemas de informação de protocolo em plataforma web (sproweb).</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2014NE00030</t>
+          <t>2014NE00028</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>6/2011</t>
+          <t>2/2011</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4660,7 +4660,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1957.1</v>
+        <v>39648.7</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -4669,19 +4669,19 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Contrato No. 6/2011 - Sistema Controle de Pessoal - CPBM</t>
+          <t>Contrato No. 2/2011 - Acesso Computador Central Tecnologia VPN, Internet 1,2 Mbps</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2014NE00028</t>
+          <t>2014NE00030</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2/2011</t>
+          <t>6/2011</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>39648.7</v>
+        <v>1957.1</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -4699,19 +4699,19 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Contrato No. 2/2011 - Acesso Computador Central Tecnologia VPN, Internet 1,2 Mbps</t>
+          <t>Contrato No. 6/2011 - Sistema Controle de Pessoal - CPBM</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2017NE01534</t>
+          <t>2017NE01535</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1/2017</t>
+          <t>5/2016</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4720,7 +4720,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>2584.09</v>
+        <v>403.52</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -4729,19 +4729,19 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE INFORMAÇÃO PARA DISPONIBILIZAÇÃO DOS SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
+          <t>PRESTAÇÃO DE SERVIÇO DE MANUTENÇÃO DO SISTEMA DE PROCESSAMENTO DE CONTROLE DE PESSOAL DA DIRETORIA DE RECURSOS HUMANOS DO CBMAM</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2017NE01535</t>
+          <t>2017NE01534</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5/2016</t>
+          <t>1/2017</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4750,7 +4750,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>403.52</v>
+        <v>2584.09</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>PRESTAÇÃO DE SERVIÇO DE MANUTENÇÃO DO SISTEMA DE PROCESSAMENTO DE CONTROLE DE PESSOAL DA DIRETORIA DE RECURSOS HUMANOS DO CBMAM</t>
+          <t>PRESTAÇÃO DE SERVIÇOS DE EXECUÇÃO DE SISTEMA DE INFORMAÇÃO PARA DISPONIBILIZAÇÃO DOS SISTEMA DE PROTOCOLO EM PLATAFORMA WEB (SPROWEB).</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2023NE0000452</t>
+          <t>2023NE00452</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4875,14 +4875,14 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>1º Termo aditivo ao contrato 006/2021 de prorrogação de prazo por 12 meses e reajuste de valor de 14,77%. Serviços especializados para o funcionamento e manutenção do sistema do processamento do contr</t>
+          <t>1º TA Contrato 006/2021 - Processamento do Controle de Pessoal</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2023NE00452</t>
+          <t>2023NE0000452</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>1º TA Contrato 006/2021 - Processamento do Controle de Pessoal</t>
+          <t>1º Termo aditivo ao contrato 006/2021 de prorrogação de prazo por 12 meses e reajuste de valor de 14,77%. Serviços especializados para o funcionamento e manutenção do sistema do processamento do contr</t>
         </is>
       </c>
     </row>

--- a/DOSSIES_MULTIFORMATO/CBMAM/dossie.xlsx
+++ b/DOSSIES_MULTIFORMATO/CBMAM/dossie.xlsx
@@ -583,7 +583,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2029-01-31</t>
         </is>
       </c>
     </row>
